--- a/docs/procurement_study/chair-SAM3D-cloud.xlsx
+++ b/docs/procurement_study/chair-SAM3D-cloud.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>query "stuhl metall schwarz" · 2026-07-15 22:21 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
+          <t>query "sessel barock metall schwarz" · 2026-07-15 23:14 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
         </is>
       </c>
     </row>
@@ -536,20 +536,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>SKÅLBODA Sessel</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8161</v>
+        <v>0.7921</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>5.99</v>
@@ -560,14 +560,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17.99</v>
+        <v>75.98</v>
       </c>
       <c r="K5" t="n">
-        <v>17.99</v>
+        <v>75.98</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-schwarz-30605423/</t>
+          <t>https://www.ikea.com/de/de/p/skalboda-sessel-weiss-20582035/</t>
         </is>
       </c>
     </row>
@@ -584,20 +584,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>SKÅLBODA Sessel</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8161</v>
+        <v>0.7921</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>23.96</v>
@@ -608,14 +608,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>143.96</v>
+        <v>723.86</v>
       </c>
       <c r="K6" t="n">
-        <v>14.4</v>
+        <v>72.39</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-schwarz-30605423/</t>
+          <t>https://www.ikea.com/de/de/p/skalboda-sessel-weiss-20582035/</t>
         </is>
       </c>
     </row>
@@ -651,28 +651,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>svita loungesessel freia loungestuhl metallbeine teddyboucle schwarz S0X9S0Z0</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8106</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.7936</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>5.99</v>
+        <v>5.95</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -680,14 +682,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20.99</v>
+        <v>85.94</v>
       </c>
       <c r="K8" t="n">
-        <v>20.99</v>
+        <v>85.94</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-anthrazit-remmarn-anthrazit-40605253/</t>
+          <t>https://www.otto.de/p/svita-loungesessel-freia-loungestuhl-metallbeine-teddyboucle-schwarz-S0X9S0Z0/</t>
         </is>
       </c>
     </row>
@@ -699,28 +701,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>svita loungesessel freia loungestuhl metallbeine teddyboucle schwarz S0X9S0Z0</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8106</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7936</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>23.96</v>
+        <v>23.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -728,40 +732,64 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>173.96</v>
+        <v>823.7</v>
       </c>
       <c r="K9" t="n">
-        <v>17.4</v>
+        <v>82.37</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-anthrazit-remmarn-anthrazit-40605253/</t>
+          <t>https://www.otto.de/p/svita-loungesessel-freia-loungestuhl-metallbeine-teddyboucle-schwarz-S0X9S0Z0/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IKEA Deutschland</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>ISMANTORP Sessel</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>99.98999999999999</v>
+      </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>5.99</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90 km round trip @ 0.30 €/km, one trip/order</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>parcel estimate (3/package)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.ikea.com/de/de/p/ismantorp-sessel-metall-schwarzblau-tibbleby-beigegrau-40598224/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -776,23 +804,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhl</t>
+          <t>ISMANTORP Sessel</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8236</v>
+        <v>0.8275</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>44.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>5.99</v>
+        <v>23.96</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -800,88 +828,40 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>50.98</v>
+        <v>1023.86</v>
       </c>
       <c r="K11" t="n">
-        <v>50.98</v>
+        <v>102.39</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhl-kunststoff-rot-roehrenfoermiges-metall-schwarzgrau-s29608465/</t>
+          <t>https://www.ikea.com/de/de/p/ismantorp-sessel-metall-schwarzblau-tibbleby-beigegrau-40598224/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IKEA Deutschland</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhl</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8236</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>44.99</v>
-      </c>
+          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>23.96</v>
+        <v>27</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>parcel estimate (3/package)</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>473.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhl-kunststoff-rot-roehrenfoermiges-metall-schwarzgrau-s29608465/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>27</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>90 km round trip @ 0.30 €/km, one trip/order</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -894,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -945,14 +925,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhl</t>
+          <t>EKERÖ Sessel</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8508</v>
+        <v>0.8444</v>
       </c>
       <c r="D2" t="n">
-        <v>44.99</v>
+        <v>179</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -961,26 +941,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhl-kunststoff-schwarz-profiliertes-metall-schwarzgrau-s29608470/</t>
+          <t>https://www.ikea.com/de/de/p/ekeroe-sessel-bomstad-schwarz-70494588/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhl</t>
+          <t>sessel barock sessel schwarz weiss gestreift anik repro design vintage look stueck 1 st 1e</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8374</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>69.98999999999999</v>
+        <v>489.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -989,7 +969,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhl-knaebaeck-graugruen-profiliertes-metall-schwarzgrau-s69608741/</t>
+          <t>https://www.otto.de/p/sessel-barock-sessel-schwarz-weiss-gestreift-anik-repro-design-vintage-look-stueck-1-st-1er-set-bestehend-aus-einem-sessel-material-gestell-massivholz-S0UFZ04D/</t>
         </is>
       </c>
     </row>
@@ -1001,14 +981,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>loft24 esszimmerstuhl caden set 2 st stuhl metallstuhl im retro design mit sitzhoehe 45 cm</t>
+          <t>vidaxl sessel sessel schwarz 59 x 75 x 78 cm samt 1 st CS08HM07B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8305</v>
+        <v>0.8373</v>
       </c>
       <c r="D4" t="n">
-        <v>229.99</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1017,7 +997,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/loft24-esszimmerstuhl-caden-set-2-st-stuhl-metallstuhl-im-retro-design-mit-sitzhoehe-45-cm-S0R6G0ST/</t>
+          <t>https://www.otto.de/p/vidaxl-sessel-sessel-schwarz-59-x-75-x-78-cm-samt-1-st-CS08HM07B/</t>
         </is>
       </c>
     </row>
@@ -1029,14 +1009,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MILLBERGET Drehstuhl</t>
+          <t>HERRÅKRA Sessel</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8274</v>
+        <v>0.8367</v>
       </c>
       <c r="D5" t="n">
-        <v>99.98999999999999</v>
+        <v>129</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1045,7 +1025,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/millberget-drehstuhl-murum-schwarz-70489394/</t>
+          <t>https://www.ikea.com/de/de/p/herrakra-sessel-skulsta-schwarz-20535548/</t>
         </is>
       </c>
     </row>
@@ -1057,14 +1037,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhl</t>
+          <t>ISMANTORP Sessel</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8236</v>
+        <v>0.8275</v>
       </c>
       <c r="D6" t="n">
-        <v>44.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1073,26 +1053,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhl-kunststoff-rot-roehrenfoermiges-metall-schwarzgrau-s29608465/</t>
+          <t>https://www.ikea.com/de/de/p/ismantorp-sessel-metall-schwarzblau-tibbleby-beigegrau-40598224/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOSSBERG Stuhl</t>
+          <t>sofnet ohrensessel asti 1 chesterfield sessel sofagarnitur glamour couch S0D830LR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8213</v>
+        <v>0.8234</v>
       </c>
       <c r="D7" t="n">
-        <v>79.98999999999999</v>
+        <v>369</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1101,7 +1081,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/tossberg-stuhl-metall-schwarz-gunnared-dunkelgrau-10582644/</t>
+          <t>https://www.otto.de/p/sofnet-ohrensessel-asti-1-chesterfield-sessel-sofagarnitur-glamour-couch-S0D830LR/</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1093,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>prima online stuhl metall stuhlgestell schwarz matt stabil basis modern loft 70x21cm S08D5</t>
+          <t>s style moebel chesterfield sessel whitby aus samt mit goldenen silbernen oder schwarzen f</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8175</v>
+        <v>0.8099</v>
       </c>
       <c r="D8" t="n">
-        <v>115.59</v>
+        <v>499.99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1129,7 +1109,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/prima-online-stuhl-metall-stuhlgestell-schwarz-matt-stabil-basis-modern-loft-70x21cm-S08D5008/</t>
+          <t>https://www.otto.de/p/s-style-moebel-chesterfield-sessel-whitby-aus-samt-mit-goldenen-silbernen-oder-schwarzen-fuessen-mit-wellenfederung-S05ED0HM/</t>
         </is>
       </c>
     </row>
@@ -1141,14 +1121,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>DYVLINGE Drehsessel</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8161</v>
+        <v>0.7982</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1157,26 +1137,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-schwarz-30605423/</t>
+          <t>https://www.ikea.com/de/de/p/dyvlinge-drehsessel-kelinge-schwarz-00555090/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kobolo 4 fussstuhl gartenstuhl retro black schwarz metallgestell aus taslan 1 st S0P4704M</t>
+          <t>STRANDMON Ohrensessel</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8133</v>
+        <v>0.7966</v>
       </c>
       <c r="D10" t="n">
-        <v>49.95</v>
+        <v>279</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1185,26 +1165,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/kobolo-4-fussstuhl-gartenstuhl-retro-black-schwarz-metallgestell-aus-taslan-1-st-S0P4704M/</t>
+          <t>https://www.ikea.com/de/de/p/strandmon-ohrensessel-vibberbo-schwarz-beige-20456956/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDSBERG Stuhl</t>
+          <t>svita loungesessel freia loungestuhl metallbeine teddyboucle schwarz S0X9S0Z0</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8106</v>
+        <v>0.7936</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1213,7 +1193,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/sandsberg-stuhl-anthrazit-remmarn-anthrazit-40605253/</t>
+          <t>https://www.otto.de/p/svita-loungesessel-freia-loungestuhl-metallbeine-teddyboucle-schwarz-S0X9S0Z0/</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1205,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NORDMANSSKÄR Stuhl</t>
+          <t>SKÅLBODA Sessel</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8091</v>
+        <v>0.7921</v>
       </c>
       <c r="D12" t="n">
-        <v>39.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1241,7 +1221,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/nordmansskaer-stuhl-schwarz-tonerud-grau-s99618215/</t>
+          <t>https://www.ikea.com/de/de/p/skalboda-sessel-weiss-20582035/</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1233,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lookway polsterstuhl tokio gesteppte stuhl S0VCY0C0</t>
+          <t>en casa loungesessel utsjoki 90x61x70 cm mit polsterkissen schwarz dunkelgrau S0QCY0DR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.8079</v>
+        <v>0.7811</v>
       </c>
       <c r="D13" t="n">
-        <v>109</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1269,7 +1249,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/lookway-polsterstuhl-tokio-gesteppte-stuhl-S0VCY0C0/</t>
+          <t>https://www.otto.de/p/en-casa-loungesessel-utsjoki-90x61x70-cm-mit-polsterkissen-schwarz-dunkelgrau-S0QCY0DR/</t>
         </is>
       </c>
     </row>
@@ -1281,14 +1261,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>loft24 esszimmerstuhl astrid 1 st metallstuhl modern stuhl aus metall sitzhoehe 45 cm S0LC</t>
+          <t>home affaire sessel bedford ohrensessel chesterfield mit aufwendiger knopfheftung und gesc</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8048</v>
+        <v>0.7774</v>
       </c>
       <c r="D14" t="n">
-        <v>79.98999999999999</v>
+        <v>639.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1297,7 +1277,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/loft24-esszimmerstuhl-astrid-1-st-metallstuhl-modern-stuhl-aus-metall-sitzhoehe-45-cm-S0LCG054/</t>
+          <t>https://www.otto.de/p/home-affaire-sessel-bedford-ohrensessel-chesterfield-mit-aufwendiger-knopfheftung-und-geschwungenen-armlehnen-577713931/</t>
         </is>
       </c>
     </row>
@@ -1309,14 +1289,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>riess ambiente stuhl aire schwarz einzelartikel 1 st esszimmer kunststoff metall outdoor b</t>
+          <t>s style moebel loungesessel tampa mit metall fuessen aus samtstoff hochelastischer polyure</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8037</v>
+        <v>0.777</v>
       </c>
       <c r="D15" t="n">
-        <v>49.95</v>
+        <v>379.99</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1325,26 +1305,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/riess-ambiente-stuhl-aire-schwarz-einzelartikel-1-st-esszimmer-kunststoff-metall-outdoor-balkon-S0L5G0GC/</t>
+          <t>https://www.otto.de/p/s-style-moebel-loungesessel-tampa-mit-metall-fuessen-aus-samtstoff-hochelastischer-polyurethanschaum-S0UBG0WN/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>radius esszimmerstuhl designer stuhl muse S0CEM0UT</t>
+          <t>ÖNNESTAD Sessel</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7958</v>
+        <v>0.7735</v>
       </c>
       <c r="D16" t="n">
-        <v>79.90000000000001</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1353,26 +1333,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/radius-esszimmerstuhl-designer-stuhl-muse-S0CEM0UT/</t>
+          <t>https://www.ikea.com/de/de/p/oennestad-sessel-radbyn-weiss-gruen-s09554468/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GUNDE Klappstuhl</t>
+          <t>moebel akut sessel sessel chesterfield in samt rot relaxsessel 114 cm S0NF60NP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7927</v>
+        <v>0.7611</v>
       </c>
       <c r="D17" t="n">
-        <v>12.99</v>
+        <v>369</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1381,7 +1361,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/gunde-klappstuhl-schwarz-00217797/</t>
+          <t>https://www.otto.de/p/moebel-akut-sessel-sessel-chesterfield-in-samt-rot-relaxsessel-114-cm-S0NF60NP/</t>
         </is>
       </c>
     </row>
@@ -1393,14 +1373,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SKÅLSTA Stuhluntergestell</t>
+          <t>POÄNG Sessel</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7873</v>
+        <v>0.7598</v>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1409,26 +1389,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/skalsta-stuhluntergestell-roehrenfoermig-metall-schwarzgrau-50611814/</t>
+          <t>https://www.ikea.com/de/de/p/poaeng-sessel-birkenfurnier-kelinge-graublau-s59625005/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SMÄLLEN Drehstuhl</t>
+          <t>jvmoebel sessel barock sessel im rokoko design aus schwarzem stoff mit silbernen fuessen s</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7812</v>
+        <v>0.4666</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>2309</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1437,7 +1417,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/smaellen-drehstuhl-schwarz-00503435/</t>
+          <t>https://www.otto.de/p/jvmoebel-sessel-barock-sessel-im-rokoko-design-aus-schwarzem-stoff-mit-silbernen-fuessen-sessel-made-in-europa-S0BFI0UK/</t>
         </is>
       </c>
     </row>
@@ -1449,14 +1429,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hjh office esszimmerstuhl vantaggio comfort stuhl metall ohne armlehnen 1 1 st kuechenstuh</t>
+          <t>jvmoebel sessel barock rokoko sessel hocker schwarz mit edelstahlfuessen sessel made in eu</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7793</v>
+        <v>0.4666</v>
       </c>
       <c r="D20" t="n">
-        <v>74.90000000000001</v>
+        <v>3249</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1465,35 +1445,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/hjh-office-esszimmerstuhl-vantaggio-comfort-stuhl-metall-ohne-armlehnen-1-1-st-kuechenstuhl-stuhl-esszimmer-stapelstuhl-metallgestell-S0F0L0W3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OTTO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>hti line gartenstuhl gartenstuhl curly stueck 1 st metallstuhl mit armlehnen nostalgisch S</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7776</v>
-      </c>
-      <c r="D21" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://www.otto.de/p/hti-line-gartenstuhl-gartenstuhl-curly-stueck-1-st-metallstuhl-mit-armlehnen-nostalgisch-S0Z000AD/</t>
+          <t>https://www.otto.de/p/jvmoebel-sessel-barock-rokoko-sessel-hocker-schwarz-mit-edelstahlfuessen-sessel-made-in-europa-S0DFI0BY/</t>
         </is>
       </c>
     </row>
